--- a/excel/saas_revenue_churn_analysis.xlsx
+++ b/excel/saas_revenue_churn_analysis.xlsx
@@ -6618,9 +6618,7 @@
       <x:c r="K3" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M3" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M3"/>
       <x:c r="N3">
         <x:v>1</x:v>
       </x:c>
@@ -6742,9 +6740,7 @@
       <x:c r="K5" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M5" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M5"/>
       <x:c r="N5">
         <x:v>3</x:v>
       </x:c>
@@ -6802,9 +6798,7 @@
       <x:c r="K6" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M6" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M6"/>
       <x:c r="N6">
         <x:v>3</x:v>
       </x:c>
@@ -6862,9 +6856,7 @@
       <x:c r="K7" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M7" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M7"/>
       <x:c r="N7">
         <x:v>12</x:v>
       </x:c>
@@ -7242,9 +7234,7 @@
       <x:c r="K13" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M13" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M13"/>
       <x:c r="N13">
         <x:v>4</x:v>
       </x:c>
@@ -7302,9 +7292,7 @@
       <x:c r="K14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M14" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M14"/>
       <x:c r="N14">
         <x:v>10</x:v>
       </x:c>
@@ -7746,9 +7734,7 @@
       <x:c r="K21" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M21" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M21"/>
       <x:c r="N21">
         <x:v>8</x:v>
       </x:c>
@@ -7870,9 +7856,7 @@
       <x:c r="K23" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M23" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M23"/>
       <x:c r="N23">
         <x:v>5</x:v>
       </x:c>
@@ -7994,9 +7978,7 @@
       <x:c r="K25" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M25" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M25"/>
       <x:c r="N25">
         <x:v>11</x:v>
       </x:c>
@@ -8054,9 +8036,7 @@
       <x:c r="K26" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M26" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M26"/>
       <x:c r="N26">
         <x:v>1</x:v>
       </x:c>
@@ -8114,9 +8094,7 @@
       <x:c r="K27" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M27" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M27"/>
       <x:c r="N27">
         <x:v>2</x:v>
       </x:c>
@@ -8238,9 +8216,7 @@
       <x:c r="K29" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M29" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M29"/>
       <x:c r="N29">
         <x:v>8</x:v>
       </x:c>
@@ -8362,9 +8338,7 @@
       <x:c r="K31" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M31" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M31"/>
       <x:c r="N31">
         <x:v>9</x:v>
       </x:c>
@@ -8422,9 +8396,7 @@
       <x:c r="K32" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M32" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M32"/>
       <x:c r="N32">
         <x:v>8</x:v>
       </x:c>
@@ -8482,9 +8454,7 @@
       <x:c r="K33" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M33" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M33"/>
       <x:c r="N33">
         <x:v>7</x:v>
       </x:c>
@@ -8606,9 +8576,7 @@
       <x:c r="K35" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M35" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M35"/>
       <x:c r="N35">
         <x:v>5</x:v>
       </x:c>
@@ -8922,9 +8890,7 @@
       <x:c r="K40" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M40" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M40"/>
       <x:c r="N40">
         <x:v>4</x:v>
       </x:c>
@@ -8982,9 +8948,7 @@
       <x:c r="K41" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M41" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M41"/>
       <x:c r="N41">
         <x:v>9</x:v>
       </x:c>
@@ -9106,9 +9070,7 @@
       <x:c r="K43" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M43" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M43"/>
       <x:c r="N43">
         <x:v>9</x:v>
       </x:c>
@@ -9166,9 +9128,7 @@
       <x:c r="K44" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M44" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M44"/>
       <x:c r="N44">
         <x:v>9</x:v>
       </x:c>
@@ -9290,9 +9250,7 @@
       <x:c r="K46" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M46" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M46"/>
       <x:c r="N46">
         <x:v>12</x:v>
       </x:c>
@@ -9862,9 +9820,7 @@
       <x:c r="K55" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M55" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M55"/>
       <x:c r="N55">
         <x:v>4</x:v>
       </x:c>
@@ -10434,9 +10390,7 @@
       <x:c r="K64" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M64" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M64"/>
       <x:c r="N64">
         <x:v>3</x:v>
       </x:c>
@@ -10494,9 +10448,7 @@
       <x:c r="K65" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M65" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M65"/>
       <x:c r="N65">
         <x:v>1</x:v>
       </x:c>
@@ -10682,9 +10634,7 @@
       <x:c r="K68" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M68" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M68"/>
       <x:c r="N68">
         <x:v>4</x:v>
       </x:c>
@@ -10742,9 +10692,7 @@
       <x:c r="K69" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M69" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M69"/>
       <x:c r="N69">
         <x:v>7</x:v>
       </x:c>
@@ -10931,9 +10879,7 @@
       <x:c r="K72" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M72" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M72"/>
       <x:c r="N72">
         <x:v>4</x:v>
       </x:c>
@@ -10991,9 +10937,7 @@
       <x:c r="K73" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M73" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M73"/>
       <x:c r="N73">
         <x:v>7</x:v>
       </x:c>
@@ -11051,9 +10995,7 @@
       <x:c r="K74" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M74" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M74"/>
       <x:c r="N74">
         <x:v>7</x:v>
       </x:c>
@@ -11175,9 +11117,7 @@
       <x:c r="K76" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M76" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M76"/>
       <x:c r="N76">
         <x:v>5</x:v>
       </x:c>
@@ -11235,9 +11175,7 @@
       <x:c r="K77" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M77" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M77"/>
       <x:c r="N77">
         <x:v>2</x:v>
       </x:c>
@@ -11295,9 +11233,7 @@
       <x:c r="K78" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M78" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M78"/>
       <x:c r="N78">
         <x:v>4</x:v>
       </x:c>
@@ -11419,9 +11355,7 @@
       <x:c r="K80" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M80" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M80"/>
       <x:c r="N80">
         <x:v>0</x:v>
       </x:c>
@@ -11544,9 +11478,7 @@
       <x:c r="K82" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M82" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M82"/>
       <x:c r="N82">
         <x:v>2</x:v>
       </x:c>
@@ -11668,9 +11600,7 @@
       <x:c r="K84" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M84" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M84"/>
       <x:c r="N84">
         <x:v>6</x:v>
       </x:c>
@@ -11856,9 +11786,7 @@
       <x:c r="K87" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M87" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M87"/>
       <x:c r="N87">
         <x:v>9</x:v>
       </x:c>
@@ -11916,9 +11844,7 @@
       <x:c r="K88" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M88" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M88"/>
       <x:c r="N88">
         <x:v>2</x:v>
       </x:c>
@@ -12232,9 +12158,7 @@
       <x:c r="K93" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M93" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M93"/>
       <x:c r="N93">
         <x:v>7</x:v>
       </x:c>
@@ -12292,9 +12216,7 @@
       <x:c r="K94" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M94" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M94"/>
       <x:c r="N94">
         <x:v>2</x:v>
       </x:c>
@@ -12544,9 +12466,7 @@
       <x:c r="K98" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M98" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M98"/>
       <x:c r="N98">
         <x:v>1</x:v>
       </x:c>
@@ -12669,9 +12589,7 @@
       <x:c r="K100" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M100" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M100"/>
       <x:c r="N100">
         <x:v>3</x:v>
       </x:c>
@@ -12729,9 +12647,7 @@
       <x:c r="K101" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M101" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M101"/>
       <x:c r="N101">
         <x:v>1</x:v>
       </x:c>
@@ -12854,9 +12770,7 @@
       <x:c r="K103" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M103" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M103"/>
       <x:c r="N103">
         <x:v>11</x:v>
       </x:c>
@@ -12914,9 +12828,7 @@
       <x:c r="K104" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M104" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M104"/>
       <x:c r="N104">
         <x:v>0</x:v>
       </x:c>
@@ -13038,9 +12950,7 @@
       <x:c r="K106" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M106" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M106"/>
       <x:c r="N106">
         <x:v>6</x:v>
       </x:c>
@@ -13226,9 +13136,7 @@
       <x:c r="K109" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M109" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M109"/>
       <x:c r="N109">
         <x:v>11</x:v>
       </x:c>
@@ -13286,9 +13194,7 @@
       <x:c r="K110" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M110" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M110"/>
       <x:c r="N110">
         <x:v>0</x:v>
       </x:c>
@@ -13666,9 +13572,7 @@
       <x:c r="K116" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M116" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M116"/>
       <x:c r="N116">
         <x:v>0</x:v>
       </x:c>
@@ -13726,9 +13630,7 @@
       <x:c r="K117" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M117" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M117"/>
       <x:c r="N117">
         <x:v>0</x:v>
       </x:c>
@@ -13915,9 +13817,7 @@
       <x:c r="K120" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M120" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M120"/>
       <x:c r="N120">
         <x:v>9</x:v>
       </x:c>
@@ -13975,9 +13875,7 @@
       <x:c r="K121" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M121" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M121"/>
       <x:c r="N121">
         <x:v>3</x:v>
       </x:c>
@@ -14036,9 +13934,7 @@
       <x:c r="K122" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M122" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M122"/>
       <x:c r="N122">
         <x:v>6</x:v>
       </x:c>
@@ -14096,9 +13992,7 @@
       <x:c r="K123" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M123" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M123"/>
       <x:c r="N123">
         <x:v>4</x:v>
       </x:c>
@@ -14156,9 +14050,7 @@
       <x:c r="K124" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M124" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M124"/>
       <x:c r="N124">
         <x:v>4</x:v>
       </x:c>
@@ -14216,9 +14108,7 @@
       <x:c r="K125" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M125" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M125"/>
       <x:c r="N125">
         <x:v>2</x:v>
       </x:c>
@@ -14276,9 +14166,7 @@
       <x:c r="K126" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M126" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M126"/>
       <x:c r="N126">
         <x:v>11</x:v>
       </x:c>
@@ -14336,9 +14224,7 @@
       <x:c r="K127" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M127" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M127"/>
       <x:c r="N127">
         <x:v>1</x:v>
       </x:c>
@@ -14588,9 +14474,7 @@
       <x:c r="K131" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M131" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M131"/>
       <x:c r="N131">
         <x:v>6</x:v>
       </x:c>
@@ -14648,9 +14532,7 @@
       <x:c r="K132" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M132" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M132"/>
       <x:c r="N132">
         <x:v>11</x:v>
       </x:c>
@@ -14708,9 +14590,7 @@
       <x:c r="K133" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M133" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M133"/>
       <x:c r="N133">
         <x:v>7</x:v>
       </x:c>
@@ -14768,9 +14648,7 @@
       <x:c r="K134" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M134" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M134"/>
       <x:c r="N134">
         <x:v>7</x:v>
       </x:c>
@@ -14892,9 +14770,7 @@
       <x:c r="K136" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M136" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M136"/>
       <x:c r="N136">
         <x:v>5</x:v>
       </x:c>
@@ -14952,9 +14828,7 @@
       <x:c r="K137" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M137" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M137"/>
       <x:c r="N137">
         <x:v>4</x:v>
       </x:c>
@@ -15268,9 +15142,7 @@
       <x:c r="K142" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M142" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M142"/>
       <x:c r="N142">
         <x:v>8</x:v>
       </x:c>
@@ -15329,9 +15201,7 @@
       <x:c r="K143" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M143" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M143"/>
       <x:c r="N143">
         <x:v>8</x:v>
       </x:c>
@@ -15390,9 +15260,7 @@
       <x:c r="K144" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M144" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M144"/>
       <x:c r="N144">
         <x:v>12</x:v>
       </x:c>
@@ -15578,9 +15446,7 @@
       <x:c r="K147" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M147" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M147"/>
       <x:c r="N147">
         <x:v>1</x:v>
       </x:c>
@@ -15702,9 +15568,7 @@
       <x:c r="K149" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M149" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M149"/>
       <x:c r="N149">
         <x:v>5</x:v>
       </x:c>
@@ -15762,9 +15626,7 @@
       <x:c r="K150" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M150" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M150"/>
       <x:c r="N150">
         <x:v>11</x:v>
       </x:c>
@@ -16206,9 +16068,7 @@
       <x:c r="K157" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M157" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M157"/>
       <x:c r="N157">
         <x:v>4</x:v>
       </x:c>
@@ -16266,9 +16126,7 @@
       <x:c r="K158" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M158" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M158"/>
       <x:c r="N158">
         <x:v>9</x:v>
       </x:c>
@@ -16326,9 +16184,7 @@
       <x:c r="K159" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M159" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M159"/>
       <x:c r="N159">
         <x:v>6</x:v>
       </x:c>
@@ -16387,9 +16243,7 @@
       <x:c r="K160" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M160" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M160"/>
       <x:c r="N160">
         <x:v>8</x:v>
       </x:c>
@@ -16447,9 +16301,7 @@
       <x:c r="K161" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M161" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M161"/>
       <x:c r="N161">
         <x:v>9</x:v>
       </x:c>
@@ -16635,9 +16487,7 @@
       <x:c r="K164" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M164" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M164"/>
       <x:c r="N164">
         <x:v>3</x:v>
       </x:c>
@@ -16759,9 +16609,7 @@
       <x:c r="K166" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M166" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M166"/>
       <x:c r="N166">
         <x:v>12</x:v>
       </x:c>
@@ -16883,9 +16731,7 @@
       <x:c r="K168" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M168" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M168"/>
       <x:c r="N168">
         <x:v>10</x:v>
       </x:c>
@@ -17007,9 +16853,7 @@
       <x:c r="K170" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M170" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M170"/>
       <x:c r="N170">
         <x:v>0</x:v>
       </x:c>
@@ -17067,9 +16911,7 @@
       <x:c r="K171" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M171" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M171"/>
       <x:c r="N171">
         <x:v>1</x:v>
       </x:c>
@@ -17255,9 +17097,7 @@
       <x:c r="K174" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M174" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M174"/>
       <x:c r="N174">
         <x:v>12</x:v>
       </x:c>
@@ -17315,9 +17155,7 @@
       <x:c r="K175" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M175" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M175"/>
       <x:c r="N175">
         <x:v>10</x:v>
       </x:c>
@@ -17375,9 +17213,7 @@
       <x:c r="K176" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M176" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M176"/>
       <x:c r="N176">
         <x:v>12</x:v>
       </x:c>
@@ -17563,9 +17399,7 @@
       <x:c r="K179" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M179" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M179"/>
       <x:c r="N179">
         <x:v>4</x:v>
       </x:c>
@@ -17623,9 +17457,7 @@
       <x:c r="K180" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M180" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M180"/>
       <x:c r="N180">
         <x:v>3</x:v>
       </x:c>
@@ -17811,9 +17643,7 @@
       <x:c r="K183" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M183" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M183"/>
       <x:c r="N183">
         <x:v>9</x:v>
       </x:c>
@@ -17935,9 +17765,7 @@
       <x:c r="K185" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M185" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M185"/>
       <x:c r="N185">
         <x:v>8</x:v>
       </x:c>
@@ -17995,9 +17823,7 @@
       <x:c r="K186" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M186" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M186"/>
       <x:c r="N186">
         <x:v>3</x:v>
       </x:c>
@@ -18247,9 +18073,7 @@
       <x:c r="K190" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M190" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M190"/>
       <x:c r="N190">
         <x:v>11</x:v>
       </x:c>
@@ -18307,9 +18131,7 @@
       <x:c r="K191" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M191" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M191"/>
       <x:c r="N191">
         <x:v>7</x:v>
       </x:c>
@@ -18431,9 +18253,7 @@
       <x:c r="K193" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M193" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M193"/>
       <x:c r="N193">
         <x:v>8</x:v>
       </x:c>
@@ -18491,9 +18311,7 @@
       <x:c r="K194" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M194" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M194"/>
       <x:c r="N194">
         <x:v>0</x:v>
       </x:c>
@@ -18551,9 +18369,7 @@
       <x:c r="K195" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M195" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M195"/>
       <x:c r="N195">
         <x:v>6</x:v>
       </x:c>
@@ -18675,9 +18491,7 @@
       <x:c r="K197" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M197" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M197"/>
       <x:c r="N197">
         <x:v>6</x:v>
       </x:c>
@@ -18735,9 +18549,7 @@
       <x:c r="K198" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M198" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M198"/>
       <x:c r="N198">
         <x:v>8</x:v>
       </x:c>
@@ -18859,9 +18671,7 @@
       <x:c r="K200" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M200" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M200"/>
       <x:c r="N200">
         <x:v>2</x:v>
       </x:c>
@@ -19240,9 +19050,7 @@
       <x:c r="K206" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M206" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M206"/>
       <x:c r="N206">
         <x:v>12</x:v>
       </x:c>
@@ -19620,9 +19428,7 @@
       <x:c r="K212" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M212" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M212"/>
       <x:c r="N212">
         <x:v>12</x:v>
       </x:c>
@@ -19681,9 +19487,7 @@
       <x:c r="K213" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M213" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M213"/>
       <x:c r="N213">
         <x:v>1</x:v>
       </x:c>
@@ -19741,9 +19545,7 @@
       <x:c r="K214" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M214" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M214"/>
       <x:c r="N214">
         <x:v>4</x:v>
       </x:c>
@@ -19994,9 +19796,7 @@
       <x:c r="K218" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M218" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M218"/>
       <x:c r="N218">
         <x:v>3</x:v>
       </x:c>
@@ -20118,9 +19918,7 @@
       <x:c r="K220" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M220" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M220"/>
       <x:c r="N220">
         <x:v>6</x:v>
       </x:c>
@@ -20242,9 +20040,7 @@
       <x:c r="K222" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M222" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M222"/>
       <x:c r="N222">
         <x:v>7</x:v>
       </x:c>
@@ -20302,9 +20098,7 @@
       <x:c r="K223" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M223" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M223"/>
       <x:c r="N223">
         <x:v>6</x:v>
       </x:c>
@@ -20490,9 +20284,7 @@
       <x:c r="K226" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M226" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M226"/>
       <x:c r="N226">
         <x:v>7</x:v>
       </x:c>
@@ -20551,9 +20343,7 @@
       <x:c r="K227" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M227" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M227"/>
       <x:c r="N227">
         <x:v>10</x:v>
       </x:c>
@@ -20675,9 +20465,7 @@
       <x:c r="K229" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M229" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M229"/>
       <x:c r="N229">
         <x:v>8</x:v>
       </x:c>
@@ -20735,9 +20523,7 @@
       <x:c r="K230" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M230" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M230"/>
       <x:c r="N230">
         <x:v>0</x:v>
       </x:c>
@@ -20859,9 +20645,7 @@
       <x:c r="K232" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M232" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M232"/>
       <x:c r="N232">
         <x:v>4</x:v>
       </x:c>
@@ -20919,9 +20703,7 @@
       <x:c r="K233" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M233" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M233"/>
       <x:c r="N233">
         <x:v>9</x:v>
       </x:c>
@@ -20979,9 +20761,7 @@
       <x:c r="K234" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M234" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M234"/>
       <x:c r="N234">
         <x:v>0</x:v>
       </x:c>
@@ -21103,9 +20883,7 @@
       <x:c r="K236" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M236" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M236"/>
       <x:c r="N236">
         <x:v>6</x:v>
       </x:c>
@@ -21227,9 +21005,7 @@
       <x:c r="K238" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M238" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M238"/>
       <x:c r="N238">
         <x:v>0</x:v>
       </x:c>
@@ -21288,9 +21064,7 @@
       <x:c r="K239" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M239" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M239"/>
       <x:c r="N239">
         <x:v>12</x:v>
       </x:c>
@@ -21412,9 +21186,7 @@
       <x:c r="K241" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M241" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M241"/>
       <x:c r="N241">
         <x:v>6</x:v>
       </x:c>
@@ -21537,9 +21309,7 @@
       <x:c r="K243" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M243" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M243"/>
       <x:c r="N243">
         <x:v>1</x:v>
       </x:c>
@@ -21597,9 +21367,7 @@
       <x:c r="K244" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M244" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M244"/>
       <x:c r="N244">
         <x:v>4</x:v>
       </x:c>
@@ -21721,9 +21489,7 @@
       <x:c r="K246" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M246" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M246"/>
       <x:c r="N246">
         <x:v>5</x:v>
       </x:c>
@@ -21846,9 +21612,7 @@
       <x:c r="K248" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M248" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M248"/>
       <x:c r="N248">
         <x:v>10</x:v>
       </x:c>
@@ -22034,9 +21798,7 @@
       <x:c r="K251" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M251" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M251"/>
       <x:c r="N251">
         <x:v>1</x:v>
       </x:c>
@@ -22286,9 +22048,7 @@
       <x:c r="K255" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M255" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M255"/>
       <x:c r="N255">
         <x:v>0</x:v>
       </x:c>
@@ -22410,9 +22170,7 @@
       <x:c r="K257" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M257" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M257"/>
       <x:c r="N257">
         <x:v>10</x:v>
       </x:c>
@@ -22470,9 +22228,7 @@
       <x:c r="K258" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M258" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M258"/>
       <x:c r="N258">
         <x:v>2</x:v>
       </x:c>
@@ -22594,9 +22350,7 @@
       <x:c r="K260" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M260" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M260"/>
       <x:c r="N260">
         <x:v>3</x:v>
       </x:c>
@@ -22718,9 +22472,7 @@
       <x:c r="K262" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M262" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M262"/>
       <x:c r="N262">
         <x:v>1</x:v>
       </x:c>
@@ -22842,9 +22594,7 @@
       <x:c r="K264" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M264" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M264"/>
       <x:c r="N264">
         <x:v>3</x:v>
       </x:c>
@@ -22902,9 +22652,7 @@
       <x:c r="K265" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M265" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M265"/>
       <x:c r="N265">
         <x:v>2</x:v>
       </x:c>
@@ -22962,9 +22710,7 @@
       <x:c r="K266" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M266" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M266"/>
       <x:c r="N266">
         <x:v>11</x:v>
       </x:c>
@@ -23086,9 +22832,7 @@
       <x:c r="K268" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M268" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M268"/>
       <x:c r="N268">
         <x:v>3</x:v>
       </x:c>
@@ -23146,9 +22890,7 @@
       <x:c r="K269" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M269" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M269"/>
       <x:c r="N269">
         <x:v>12</x:v>
       </x:c>
@@ -23462,9 +23204,7 @@
       <x:c r="K274" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M274" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M274"/>
       <x:c r="N274">
         <x:v>2</x:v>
       </x:c>
@@ -23522,9 +23262,7 @@
       <x:c r="K275" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M275" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M275"/>
       <x:c r="N275">
         <x:v>2</x:v>
       </x:c>
@@ -23582,9 +23320,7 @@
       <x:c r="K276" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M276" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M276"/>
       <x:c r="N276">
         <x:v>7</x:v>
       </x:c>
@@ -23642,9 +23378,7 @@
       <x:c r="K277" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M277" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M277"/>
       <x:c r="N277">
         <x:v>0</x:v>
       </x:c>
@@ -23766,9 +23500,7 @@
       <x:c r="K279" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M279" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M279"/>
       <x:c r="N279">
         <x:v>7</x:v>
       </x:c>
@@ -23826,9 +23558,7 @@
       <x:c r="K280" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M280" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M280"/>
       <x:c r="N280">
         <x:v>4</x:v>
       </x:c>
@@ -23886,9 +23616,7 @@
       <x:c r="K281" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M281" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M281"/>
       <x:c r="N281">
         <x:v>2</x:v>
       </x:c>
@@ -23946,9 +23674,7 @@
       <x:c r="K282" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M282" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M282"/>
       <x:c r="N282">
         <x:v>4</x:v>
       </x:c>
@@ -24006,9 +23732,7 @@
       <x:c r="K283" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M283" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M283"/>
       <x:c r="N283">
         <x:v>1</x:v>
       </x:c>
@@ -24130,9 +23854,7 @@
       <x:c r="K285" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M285" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M285"/>
       <x:c r="N285">
         <x:v>10</x:v>
       </x:c>
@@ -24190,9 +23912,7 @@
       <x:c r="K286" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M286" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M286"/>
       <x:c r="N286">
         <x:v>9</x:v>
       </x:c>
@@ -24314,9 +24034,7 @@
       <x:c r="K288" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M288" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M288"/>
       <x:c r="N288">
         <x:v>9</x:v>
       </x:c>
@@ -24374,9 +24092,7 @@
       <x:c r="K289" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M289" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M289"/>
       <x:c r="N289">
         <x:v>12</x:v>
       </x:c>
@@ -24434,9 +24150,7 @@
       <x:c r="K290" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M290" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M290"/>
       <x:c r="N290">
         <x:v>3</x:v>
       </x:c>
@@ -24558,9 +24272,7 @@
       <x:c r="K292" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M292" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M292"/>
       <x:c r="N292">
         <x:v>9</x:v>
       </x:c>
@@ -24938,9 +24650,7 @@
       <x:c r="K298" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M298" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M298"/>
       <x:c r="N298">
         <x:v>6</x:v>
       </x:c>
@@ -25126,9 +24836,7 @@
       <x:c r="K301" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M301" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M301"/>
       <x:c r="N301">
         <x:v>11</x:v>
       </x:c>
@@ -25186,9 +24894,7 @@
       <x:c r="K302" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M302" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M302"/>
       <x:c r="N302">
         <x:v>3</x:v>
       </x:c>
@@ -25246,9 +24952,7 @@
       <x:c r="K303" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M303" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M303"/>
       <x:c r="N303">
         <x:v>8</x:v>
       </x:c>
@@ -25434,9 +25138,7 @@
       <x:c r="K306" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M306" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M306"/>
       <x:c r="N306">
         <x:v>8</x:v>
       </x:c>
@@ -25494,9 +25196,7 @@
       <x:c r="K307" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M307" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M307"/>
       <x:c r="N307">
         <x:v>4</x:v>
       </x:c>
@@ -25554,9 +25254,7 @@
       <x:c r="K308" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M308" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M308"/>
       <x:c r="N308">
         <x:v>9</x:v>
       </x:c>
@@ -25614,9 +25312,7 @@
       <x:c r="K309" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M309" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M309"/>
       <x:c r="N309">
         <x:v>0</x:v>
       </x:c>
@@ -25802,9 +25498,7 @@
       <x:c r="K312" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M312" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M312"/>
       <x:c r="N312">
         <x:v>9</x:v>
       </x:c>
@@ -25926,9 +25620,7 @@
       <x:c r="K314" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M314" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M314"/>
       <x:c r="N314">
         <x:v>3</x:v>
       </x:c>
@@ -25987,9 +25679,7 @@
       <x:c r="K315" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M315" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M315"/>
       <x:c r="N315">
         <x:v>3</x:v>
       </x:c>
@@ -26368,9 +26058,7 @@
       <x:c r="K321" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M321" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M321"/>
       <x:c r="N321">
         <x:v>10</x:v>
       </x:c>
@@ -26556,9 +26244,7 @@
       <x:c r="K324" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M324" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M324"/>
       <x:c r="N324">
         <x:v>5</x:v>
       </x:c>
@@ -26616,9 +26302,7 @@
       <x:c r="K325" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M325" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M325"/>
       <x:c r="N325">
         <x:v>7</x:v>
       </x:c>
@@ -26740,9 +26424,7 @@
       <x:c r="K327" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M327" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M327"/>
       <x:c r="N327">
         <x:v>6</x:v>
       </x:c>
@@ -26864,9 +26546,7 @@
       <x:c r="K329" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M329" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M329"/>
       <x:c r="N329">
         <x:v>2</x:v>
       </x:c>
@@ -26924,9 +26604,7 @@
       <x:c r="K330" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M330" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M330"/>
       <x:c r="N330">
         <x:v>7</x:v>
       </x:c>
@@ -26984,9 +26662,7 @@
       <x:c r="K331" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M331" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M331"/>
       <x:c r="N331">
         <x:v>7</x:v>
       </x:c>
@@ -27044,9 +26720,7 @@
       <x:c r="K332" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M332" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M332"/>
       <x:c r="N332">
         <x:v>11</x:v>
       </x:c>
@@ -27488,9 +27162,7 @@
       <x:c r="K339" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M339" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M339"/>
       <x:c r="N339">
         <x:v>4</x:v>
       </x:c>
@@ -27932,9 +27604,7 @@
       <x:c r="K346" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M346" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M346"/>
       <x:c r="N346">
         <x:v>4</x:v>
       </x:c>
@@ -27992,9 +27662,7 @@
       <x:c r="K347" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M347" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M347"/>
       <x:c r="N347">
         <x:v>9</x:v>
       </x:c>
@@ -28052,9 +27720,7 @@
       <x:c r="K348" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M348" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M348"/>
       <x:c r="N348">
         <x:v>5</x:v>
       </x:c>
@@ -28113,9 +27779,7 @@
       <x:c r="K349" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M349" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M349"/>
       <x:c r="N349">
         <x:v>9</x:v>
       </x:c>
@@ -28173,9 +27837,7 @@
       <x:c r="K350" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M350" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M350"/>
       <x:c r="N350">
         <x:v>7</x:v>
       </x:c>
@@ -28553,9 +28215,7 @@
       <x:c r="K356" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M356" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M356"/>
       <x:c r="N356">
         <x:v>3</x:v>
       </x:c>
@@ -28741,9 +28401,7 @@
       <x:c r="K359" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M359" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M359"/>
       <x:c r="N359">
         <x:v>1</x:v>
       </x:c>
@@ -28801,9 +28459,7 @@
       <x:c r="K360" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M360" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M360"/>
       <x:c r="N360">
         <x:v>10</x:v>
       </x:c>
@@ -28861,9 +28517,7 @@
       <x:c r="K361" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M361" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M361"/>
       <x:c r="N361">
         <x:v>11</x:v>
       </x:c>
@@ -28921,9 +28575,7 @@
       <x:c r="K362" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M362" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M362"/>
       <x:c r="N362">
         <x:v>12</x:v>
       </x:c>
@@ -28981,9 +28633,7 @@
       <x:c r="K363" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M363" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M363"/>
       <x:c r="N363">
         <x:v>0</x:v>
       </x:c>
@@ -29041,9 +28691,7 @@
       <x:c r="K364" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M364" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M364"/>
       <x:c r="N364">
         <x:v>2</x:v>
       </x:c>
@@ -29229,9 +28877,7 @@
       <x:c r="K367" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M367" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M367"/>
       <x:c r="N367">
         <x:v>11</x:v>
       </x:c>
@@ -29289,9 +28935,7 @@
       <x:c r="K368" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M368" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M368"/>
       <x:c r="N368">
         <x:v>1</x:v>
       </x:c>
@@ -29349,9 +28993,7 @@
       <x:c r="K369" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M369" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M369"/>
       <x:c r="N369">
         <x:v>3</x:v>
       </x:c>
@@ -29665,9 +29307,7 @@
       <x:c r="K374" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M374" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M374"/>
       <x:c r="N374">
         <x:v>6</x:v>
       </x:c>
@@ -30109,9 +29749,7 @@
       <x:c r="K381" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M381" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M381"/>
       <x:c r="N381">
         <x:v>7</x:v>
       </x:c>
@@ -30169,9 +29807,7 @@
       <x:c r="K382" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M382" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M382"/>
       <x:c r="N382">
         <x:v>11</x:v>
       </x:c>
@@ -30357,9 +29993,7 @@
       <x:c r="K385" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M385" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M385"/>
       <x:c r="N385">
         <x:v>6</x:v>
       </x:c>
@@ -30609,9 +30243,7 @@
       <x:c r="K389" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M389" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M389"/>
       <x:c r="N389">
         <x:v>11</x:v>
       </x:c>
@@ -30669,9 +30301,7 @@
       <x:c r="K390" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M390" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M390"/>
       <x:c r="N390">
         <x:v>7</x:v>
       </x:c>
@@ -30921,9 +30551,7 @@
       <x:c r="K394" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M394" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M394"/>
       <x:c r="N394">
         <x:v>1</x:v>
       </x:c>
@@ -30981,9 +30609,7 @@
       <x:c r="K395" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M395" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M395"/>
       <x:c r="N395">
         <x:v>5</x:v>
       </x:c>
@@ -31041,9 +30667,7 @@
       <x:c r="K396" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M396" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M396"/>
       <x:c r="N396">
         <x:v>0</x:v>
       </x:c>
@@ -31102,9 +30726,7 @@
       <x:c r="K397" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M397" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M397"/>
       <x:c r="N397">
         <x:v>3</x:v>
       </x:c>
@@ -31418,9 +31040,7 @@
       <x:c r="K402" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M402" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M402"/>
       <x:c r="N402">
         <x:v>9</x:v>
       </x:c>
@@ -31606,9 +31226,7 @@
       <x:c r="K405" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M405" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M405"/>
       <x:c r="N405">
         <x:v>4</x:v>
       </x:c>
@@ -31666,9 +31284,7 @@
       <x:c r="K406" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M406" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M406"/>
       <x:c r="N406">
         <x:v>11</x:v>
       </x:c>
@@ -31855,9 +31471,7 @@
       <x:c r="K409" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M409" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M409"/>
       <x:c r="N409">
         <x:v>10</x:v>
       </x:c>
@@ -32171,9 +31785,7 @@
       <x:c r="K414" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M414" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M414"/>
       <x:c r="N414">
         <x:v>0</x:v>
       </x:c>
@@ -32551,9 +32163,7 @@
       <x:c r="K420" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M420" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M420"/>
       <x:c r="N420">
         <x:v>2</x:v>
       </x:c>
@@ -32739,9 +32349,7 @@
       <x:c r="K423" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M423" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M423"/>
       <x:c r="N423">
         <x:v>3</x:v>
       </x:c>
@@ -32991,9 +32599,7 @@
       <x:c r="K427" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M427" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M427"/>
       <x:c r="N427">
         <x:v>10</x:v>
       </x:c>
@@ -33051,9 +32657,7 @@
       <x:c r="K428" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M428" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M428"/>
       <x:c r="N428">
         <x:v>6</x:v>
       </x:c>
@@ -33111,9 +32715,7 @@
       <x:c r="K429" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M429" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M429"/>
       <x:c r="N429">
         <x:v>1</x:v>
       </x:c>
@@ -33172,9 +32774,7 @@
       <x:c r="K430" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M430" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M430"/>
       <x:c r="N430">
         <x:v>8</x:v>
       </x:c>
@@ -33232,9 +32832,7 @@
       <x:c r="K431" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M431" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M431"/>
       <x:c r="N431">
         <x:v>2</x:v>
       </x:c>
@@ -33292,9 +32890,7 @@
       <x:c r="K432" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M432" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M432"/>
       <x:c r="N432">
         <x:v>3</x:v>
       </x:c>
@@ -33352,9 +32948,7 @@
       <x:c r="K433" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M433" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M433"/>
       <x:c r="N433">
         <x:v>2</x:v>
       </x:c>
@@ -33860,9 +33454,7 @@
       <x:c r="K441" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M441" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M441"/>
       <x:c r="N441">
         <x:v>1</x:v>
       </x:c>
@@ -33984,9 +33576,7 @@
       <x:c r="K443" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M443" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M443"/>
       <x:c r="N443">
         <x:v>10</x:v>
       </x:c>
@@ -34044,9 +33634,7 @@
       <x:c r="K444" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M444" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M444"/>
       <x:c r="N444">
         <x:v>11</x:v>
       </x:c>
@@ -34104,9 +33692,7 @@
       <x:c r="K445" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M445" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M445"/>
       <x:c r="N445">
         <x:v>9</x:v>
       </x:c>
@@ -34164,9 +33750,7 @@
       <x:c r="K446" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M446" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M446"/>
       <x:c r="N446">
         <x:v>2</x:v>
       </x:c>
@@ -34288,9 +33872,7 @@
       <x:c r="K448" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M448" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M448"/>
       <x:c r="N448">
         <x:v>0</x:v>
       </x:c>
@@ -34348,9 +33930,7 @@
       <x:c r="K449" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M449" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M449"/>
       <x:c r="N449">
         <x:v>1</x:v>
       </x:c>
@@ -34472,9 +34052,7 @@
       <x:c r="K451" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M451" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M451"/>
       <x:c r="N451">
         <x:v>0</x:v>
       </x:c>
@@ -34532,9 +34110,7 @@
       <x:c r="K452" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M452" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M452"/>
       <x:c r="N452">
         <x:v>3</x:v>
       </x:c>
@@ -34592,9 +34168,7 @@
       <x:c r="K453" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M453" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M453"/>
       <x:c r="N453">
         <x:v>2</x:v>
       </x:c>
@@ -34780,9 +34354,7 @@
       <x:c r="K456" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M456" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M456"/>
       <x:c r="N456">
         <x:v>4</x:v>
       </x:c>
@@ -34840,9 +34412,7 @@
       <x:c r="K457" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M457" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M457"/>
       <x:c r="N457">
         <x:v>6</x:v>
       </x:c>
@@ -34900,9 +34470,7 @@
       <x:c r="K458" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M458" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M458"/>
       <x:c r="N458">
         <x:v>0</x:v>
       </x:c>
@@ -34960,9 +34528,7 @@
       <x:c r="K459" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M459" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M459"/>
       <x:c r="N459">
         <x:v>12</x:v>
       </x:c>
@@ -35085,9 +34651,7 @@
       <x:c r="K461" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M461" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M461"/>
       <x:c r="N461">
         <x:v>1</x:v>
       </x:c>
@@ -35145,9 +34709,7 @@
       <x:c r="K462" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M462" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M462"/>
       <x:c r="N462">
         <x:v>10</x:v>
       </x:c>
@@ -35205,9 +34767,7 @@
       <x:c r="K463" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M463" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M463"/>
       <x:c r="N463">
         <x:v>2</x:v>
       </x:c>
@@ -35329,9 +34889,7 @@
       <x:c r="K465" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M465" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M465"/>
       <x:c r="N465">
         <x:v>12</x:v>
       </x:c>
@@ -35389,9 +34947,7 @@
       <x:c r="K466" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M466" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M466"/>
       <x:c r="N466">
         <x:v>11</x:v>
       </x:c>
@@ -35449,9 +35005,7 @@
       <x:c r="K467" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M467" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M467"/>
       <x:c r="N467">
         <x:v>4</x:v>
       </x:c>
@@ -35573,9 +35127,7 @@
       <x:c r="K469" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M469" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M469"/>
       <x:c r="N469">
         <x:v>3</x:v>
       </x:c>
@@ -35633,9 +35185,7 @@
       <x:c r="K470" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M470" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M470"/>
       <x:c r="N470">
         <x:v>8</x:v>
       </x:c>
@@ -35885,9 +35435,7 @@
       <x:c r="K474" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M474" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M474"/>
       <x:c r="N474">
         <x:v>0</x:v>
       </x:c>
@@ -36009,9 +35557,7 @@
       <x:c r="K476" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M476" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M476"/>
       <x:c r="N476">
         <x:v>11</x:v>
       </x:c>
@@ -36069,9 +35615,7 @@
       <x:c r="K477" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M477" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M477"/>
       <x:c r="N477">
         <x:v>1</x:v>
       </x:c>
@@ -36130,9 +35674,7 @@
       <x:c r="K478" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M478" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M478"/>
       <x:c r="N478">
         <x:v>11</x:v>
       </x:c>
@@ -36382,9 +35924,7 @@
       <x:c r="K482" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M482" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M482"/>
       <x:c r="N482">
         <x:v>2</x:v>
       </x:c>
@@ -36442,9 +35982,7 @@
       <x:c r="K483" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M483" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M483"/>
       <x:c r="N483">
         <x:v>8</x:v>
       </x:c>
@@ -36822,9 +36360,7 @@
       <x:c r="K489" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M489" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M489"/>
       <x:c r="N489">
         <x:v>2</x:v>
       </x:c>
@@ -37138,9 +36674,7 @@
       <x:c r="K494" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M494" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M494"/>
       <x:c r="N494">
         <x:v>3</x:v>
       </x:c>
@@ -37390,9 +36924,7 @@
       <x:c r="K498" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M498" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M498"/>
       <x:c r="N498">
         <x:v>0</x:v>
       </x:c>
@@ -37450,9 +36982,7 @@
       <x:c r="K499" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M499" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M499"/>
       <x:c r="N499">
         <x:v>3</x:v>
       </x:c>
@@ -37510,9 +37040,7 @@
       <x:c r="K500" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M500" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M500"/>
       <x:c r="N500">
         <x:v>11</x:v>
       </x:c>
@@ -37570,9 +37098,7 @@
       <x:c r="K501" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M501" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M501"/>
       <x:c r="N501">
         <x:v>4</x:v>
       </x:c>
@@ -37694,9 +37220,7 @@
       <x:c r="K503" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M503" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M503"/>
       <x:c r="N503">
         <x:v>5</x:v>
       </x:c>
@@ -37754,9 +37278,7 @@
       <x:c r="K504" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M504" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M504"/>
       <x:c r="N504">
         <x:v>10</x:v>
       </x:c>
@@ -38006,9 +37528,7 @@
       <x:c r="K508" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M508" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M508"/>
       <x:c r="N508">
         <x:v>2</x:v>
       </x:c>
@@ -38258,9 +37778,7 @@
       <x:c r="K512" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M512" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M512"/>
       <x:c r="N512">
         <x:v>6</x:v>
       </x:c>
@@ -38511,9 +38029,7 @@
       <x:c r="K516" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M516" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M516"/>
       <x:c r="N516">
         <x:v>7</x:v>
       </x:c>
@@ -38571,9 +38087,7 @@
       <x:c r="K517" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M517" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M517"/>
       <x:c r="N517">
         <x:v>10</x:v>
       </x:c>
@@ -38696,9 +38210,7 @@
       <x:c r="K519" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M519" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M519"/>
       <x:c r="N519">
         <x:v>4</x:v>
       </x:c>
@@ -38756,9 +38268,7 @@
       <x:c r="K520" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M520" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M520"/>
       <x:c r="N520">
         <x:v>10</x:v>
       </x:c>
@@ -38944,9 +38454,7 @@
       <x:c r="K523" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M523" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M523"/>
       <x:c r="N523">
         <x:v>0</x:v>
       </x:c>
@@ -39068,9 +38576,7 @@
       <x:c r="K525" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M525" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M525"/>
       <x:c r="N525">
         <x:v>2</x:v>
       </x:c>
@@ -39128,9 +38634,7 @@
       <x:c r="K526" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M526" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M526"/>
       <x:c r="N526">
         <x:v>2</x:v>
       </x:c>
@@ -39252,9 +38756,7 @@
       <x:c r="K528" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M528" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M528"/>
       <x:c r="N528">
         <x:v>12</x:v>
       </x:c>
@@ -39376,9 +38878,7 @@
       <x:c r="K530" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M530" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M530"/>
       <x:c r="N530">
         <x:v>12</x:v>
       </x:c>
@@ -39436,9 +38936,7 @@
       <x:c r="K531" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M531" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M531"/>
       <x:c r="N531">
         <x:v>11</x:v>
       </x:c>
@@ -39497,9 +38995,7 @@
       <x:c r="K532" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M532" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M532"/>
       <x:c r="N532">
         <x:v>10</x:v>
       </x:c>
@@ -39557,9 +39053,7 @@
       <x:c r="K533" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M533" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M533"/>
       <x:c r="N533">
         <x:v>3</x:v>
       </x:c>
@@ -39617,9 +39111,7 @@
       <x:c r="K534" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M534" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M534"/>
       <x:c r="N534">
         <x:v>4</x:v>
       </x:c>
@@ -39741,9 +39233,7 @@
       <x:c r="K536" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M536" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M536"/>
       <x:c r="N536">
         <x:v>9</x:v>
       </x:c>
@@ -39993,9 +39483,7 @@
       <x:c r="K540" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M540" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M540"/>
       <x:c r="N540">
         <x:v>8</x:v>
       </x:c>
@@ -40181,9 +39669,7 @@
       <x:c r="K543" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M543" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M543"/>
       <x:c r="N543">
         <x:v>7</x:v>
       </x:c>
@@ -40305,9 +39791,7 @@
       <x:c r="K545" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M545" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M545"/>
       <x:c r="N545">
         <x:v>4</x:v>
       </x:c>
@@ -40558,9 +40042,7 @@
       <x:c r="K549" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M549" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M549"/>
       <x:c r="N549">
         <x:v>1</x:v>
       </x:c>
@@ -40746,9 +40228,7 @@
       <x:c r="K552" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M552" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M552"/>
       <x:c r="N552">
         <x:v>1</x:v>
       </x:c>
@@ -40806,9 +40286,7 @@
       <x:c r="K553" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M553" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M553"/>
       <x:c r="N553">
         <x:v>9</x:v>
       </x:c>
@@ -40867,9 +40345,7 @@
       <x:c r="K554" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M554" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M554"/>
       <x:c r="N554">
         <x:v>10</x:v>
       </x:c>
@@ -40991,9 +40467,7 @@
       <x:c r="K556" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M556" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M556"/>
       <x:c r="N556">
         <x:v>2</x:v>
       </x:c>
@@ -41115,9 +40589,7 @@
       <x:c r="K558" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M558" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M558"/>
       <x:c r="N558">
         <x:v>1</x:v>
       </x:c>
@@ -41175,9 +40647,7 @@
       <x:c r="K559" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M559" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M559"/>
       <x:c r="N559">
         <x:v>0</x:v>
       </x:c>
@@ -41363,9 +40833,7 @@
       <x:c r="K562" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M562" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M562"/>
       <x:c r="N562">
         <x:v>9</x:v>
       </x:c>
@@ -41423,9 +40891,7 @@
       <x:c r="K563" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M563" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M563"/>
       <x:c r="N563">
         <x:v>6</x:v>
       </x:c>
@@ -41547,9 +41013,7 @@
       <x:c r="K565" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M565" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M565"/>
       <x:c r="N565">
         <x:v>10</x:v>
       </x:c>
@@ -41799,9 +41263,7 @@
       <x:c r="K569" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M569" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M569"/>
       <x:c r="N569">
         <x:v>5</x:v>
       </x:c>
@@ -41859,9 +41321,7 @@
       <x:c r="K570" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M570" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M570"/>
       <x:c r="N570">
         <x:v>5</x:v>
       </x:c>
@@ -41919,9 +41379,7 @@
       <x:c r="K571" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M571" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M571"/>
       <x:c r="N571">
         <x:v>2</x:v>
       </x:c>
@@ -42107,9 +41565,7 @@
       <x:c r="K574" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M574" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M574"/>
       <x:c r="N574">
         <x:v>6</x:v>
       </x:c>
@@ -42167,9 +41623,7 @@
       <x:c r="K575" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M575" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M575"/>
       <x:c r="N575">
         <x:v>1</x:v>
       </x:c>
@@ -42227,9 +41681,7 @@
       <x:c r="K576" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M576" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M576"/>
       <x:c r="N576">
         <x:v>11</x:v>
       </x:c>
@@ -42479,9 +41931,7 @@
       <x:c r="K580" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M580" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M580"/>
       <x:c r="N580">
         <x:v>8</x:v>
       </x:c>
@@ -42603,9 +42053,7 @@
       <x:c r="K582" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M582" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M582"/>
       <x:c r="N582">
         <x:v>0</x:v>
       </x:c>
@@ -42791,9 +42239,7 @@
       <x:c r="K585" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M585" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M585"/>
       <x:c r="N585">
         <x:v>0</x:v>
       </x:c>
@@ -42852,9 +42298,7 @@
       <x:c r="K586" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M586" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M586"/>
       <x:c r="N586">
         <x:v>0</x:v>
       </x:c>
@@ -42912,9 +42356,7 @@
       <x:c r="K587" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M587" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M587"/>
       <x:c r="N587">
         <x:v>6</x:v>
       </x:c>
@@ -42972,9 +42414,7 @@
       <x:c r="K588" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M588" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M588"/>
       <x:c r="N588">
         <x:v>2</x:v>
       </x:c>
@@ -43224,9 +42664,7 @@
       <x:c r="K592" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M592" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M592"/>
       <x:c r="N592">
         <x:v>1</x:v>
       </x:c>
@@ -43349,9 +42787,7 @@
       <x:c r="K594" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M594" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M594"/>
       <x:c r="N594">
         <x:v>1</x:v>
       </x:c>
@@ -43537,9 +42973,7 @@
       <x:c r="K597" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M597" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M597"/>
       <x:c r="N597">
         <x:v>3</x:v>
       </x:c>
@@ -43597,9 +43031,7 @@
       <x:c r="K598" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M598" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M598"/>
       <x:c r="N598">
         <x:v>3</x:v>
       </x:c>
@@ -43657,9 +43089,7 @@
       <x:c r="K599" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M599" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M599"/>
       <x:c r="N599">
         <x:v>3</x:v>
       </x:c>
@@ -43717,9 +43147,7 @@
       <x:c r="K600" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M600" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M600"/>
       <x:c r="N600">
         <x:v>11</x:v>
       </x:c>
@@ -43777,9 +43205,7 @@
       <x:c r="K601" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="M601" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="M601"/>
       <x:c r="N601">
         <x:v>10</x:v>
       </x:c>
